--- a/E/TOY01D.xlsx
+++ b/E/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="291">
   <si>
     <t/>
   </si>
@@ -112,169 +112,766 @@
     <t>10</t>
   </si>
   <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20133202</t>
+  </si>
+  <si>
+    <t>NRTHLND DIECAST SERI</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122578</t>
+  </si>
+  <si>
+    <t>CAT LITTLE MACHINES</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20122574</t>
+  </si>
+  <si>
+    <t>H/W MONSTER TRUCK</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20102474</t>
+  </si>
+  <si>
+    <t>JRSC WORLD SNAP SQAD</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20135143</t>
+  </si>
+  <si>
+    <t>VR TOYS ALIEN SLIME</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20131019</t>
+  </si>
+  <si>
+    <t>JADA DISNEY FIGURE</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20140760</t>
+  </si>
+  <si>
+    <t>NT PARKOUR CUTE PET</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20127235</t>
+  </si>
+  <si>
+    <t>QMAN PKMON BRICK ASS</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20134674</t>
+  </si>
+  <si>
+    <t>PLYDH ESSNTL CLR 10S</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20138002</t>
+  </si>
+  <si>
+    <t>PIXAR IMPULSE  MINIS</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20132056</t>
+  </si>
+  <si>
+    <t>TROLLS BAND TGTHR FG</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20132321</t>
+  </si>
+  <si>
+    <t>VR TOY BLN AIR JMB2S</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20116479</t>
+  </si>
+  <si>
+    <t>SANRIO NECKLACE CHRT</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20131391</t>
+  </si>
+  <si>
+    <t>NRTHLND PLAYSET SERI</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20142945</t>
+  </si>
+  <si>
+    <t>EMCO METALZ PULLBACK</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20140768</t>
+  </si>
+  <si>
+    <t>NT TRAVEL PET HOME</t>
+  </si>
+  <si>
+    <t>20127783</t>
+  </si>
+  <si>
+    <t>APOLO HEAVY MACHNERY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20117276</t>
+  </si>
+  <si>
+    <t>HOT WHLS PULL BACK</t>
+  </si>
+  <si>
+    <t>20095864</t>
+  </si>
+  <si>
+    <t>WIKI D.CAST REAL CAR</t>
+  </si>
+  <si>
+    <t>20080091</t>
+  </si>
+  <si>
+    <t>APOLO MSZ PULLBACK</t>
+  </si>
+  <si>
+    <t>20142227</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY NEW S</t>
+  </si>
+  <si>
+    <t>20140758</t>
+  </si>
+  <si>
+    <t>NT MY LOVELY PET</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
     <t>20141255</t>
   </si>
   <si>
     <t>BLOKEES TRANSFORMERS</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20122578</t>
-  </si>
-  <si>
-    <t>CAT LITTLE MACHINES</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20102474</t>
-  </si>
-  <si>
-    <t>JRSC WORLD SNAP SQAD</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20122574</t>
-  </si>
-  <si>
-    <t>H/W MONSTER TRUCK</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20131019</t>
-  </si>
-  <si>
-    <t>JADA DISNEY FIGURE</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20131391</t>
-  </si>
-  <si>
-    <t>NRTHLND PLAYSET SERI</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20133202</t>
-  </si>
-  <si>
-    <t>NRTHLND DIECAST SERI</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20140760</t>
-  </si>
-  <si>
-    <t>NT PARKOUR CUTE PET</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134674</t>
-  </si>
-  <si>
-    <t>PLYDH ESSNTL CLR 10S</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20138002</t>
-  </si>
-  <si>
-    <t>PIXAR IMPULSE  MINIS</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20116479</t>
-  </si>
-  <si>
-    <t>SANRIO NECKLACE CHRT</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20127235</t>
-  </si>
-  <si>
-    <t>QMAN PKMON BRICK ASS</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20132056</t>
-  </si>
-  <si>
-    <t>TROLLS BAND TGTHR FG</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20132321</t>
-  </si>
-  <si>
-    <t>VR TOY BLN AIR JMB2S</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20135143</t>
-  </si>
-  <si>
-    <t>VR TOYS ALIEN SLIME</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
   </si>
   <si>
     <t>20141254</t>
@@ -283,610 +880,10 @@
     <t>SPNM  GABBYS DLHOUSE</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20142945</t>
-  </si>
-  <si>
-    <t>EMCO METALZ PULLBACK</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20113158</t>
-  </si>
-  <si>
-    <t>EMCO ME&amp;MY CHARMZ</t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20140768</t>
-  </si>
-  <si>
-    <t>NT TRAVEL PET HOME</t>
-  </si>
-  <si>
-    <t>20142150</t>
-  </si>
-  <si>
-    <t>BLOKEES BATMAN DV</t>
-  </si>
-  <si>
-    <t>20127783</t>
-  </si>
-  <si>
-    <t>APOLO HEAVY MACHNERY</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20117276</t>
-  </si>
-  <si>
-    <t>HOT WHLS PULL BACK</t>
-  </si>
-  <si>
-    <t>20095864</t>
-  </si>
-  <si>
-    <t>WIKI D.CAST REAL CAR</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20080091</t>
-  </si>
-  <si>
-    <t>APOLO MSZ PULLBACK</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20142227</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY NEW S</t>
-  </si>
-  <si>
-    <t>20140758</t>
-  </si>
-  <si>
-    <t>NT MY LOVELY PET</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
     <t>20133786</t>
   </si>
   <si>
     <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1727,24 +1724,24 @@
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1752,19 +1749,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1772,19 +1769,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1792,19 +1789,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1812,22 +1809,22 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,35 +2044,35 @@
         <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2084,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2092,10 +2089,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2104,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2112,10 +2109,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2124,7 +2121,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2132,10 +2129,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2144,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2152,10 +2149,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2164,10 +2161,10 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2201,30 +2198,30 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2232,10 +2229,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2244,7 +2241,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2252,10 +2249,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2264,7 +2261,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2272,10 +2269,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2284,7 +2281,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2292,10 +2289,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2304,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2312,10 +2309,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2324,7 +2321,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2332,19 +2329,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2352,19 +2349,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2372,19 +2369,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2392,10 +2389,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2404,7 +2401,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2412,10 +2409,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2424,7 +2421,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2432,10 +2429,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2444,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2452,10 +2449,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2464,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2472,10 +2469,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2484,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2492,10 +2489,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2504,7 +2501,7 @@
         <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2512,10 +2509,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2524,7 +2521,7 @@
         <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2532,10 +2529,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2552,10 +2549,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2572,10 +2569,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2584,18 +2581,18 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2604,7 +2601,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2612,10 +2609,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2624,18 +2621,18 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2644,7 +2641,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2652,10 +2649,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2664,18 +2661,18 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2684,18 +2681,18 @@
         <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2704,18 +2701,18 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2724,7 +2721,7 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2732,10 +2729,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2744,18 +2741,18 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2764,7 +2761,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2772,10 +2769,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2784,7 +2781,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2792,10 +2789,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2804,7 +2801,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2812,10 +2809,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2824,7 +2821,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2832,10 +2829,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2844,7 +2841,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2852,10 +2849,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2864,7 +2861,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2872,10 +2869,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2884,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2892,10 +2889,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2904,7 +2901,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2912,10 +2909,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2924,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2932,10 +2929,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2944,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2952,10 +2949,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2964,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2972,10 +2969,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2984,7 +2981,7 @@
         <v>17</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2992,30 +2989,30 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3024,18 +3021,18 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3044,18 +3041,18 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3067,15 +3064,15 @@
         <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3084,7 +3081,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3092,10 +3089,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3104,7 +3101,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3112,10 +3109,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3124,7 +3121,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3132,10 +3129,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3144,18 +3141,18 @@
         <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3167,15 +3164,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3184,18 +3181,18 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3204,18 +3201,18 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3224,18 +3221,18 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>237</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3244,18 +3241,18 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3264,18 +3261,18 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3284,7 +3281,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3292,10 +3289,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3304,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3309,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3324,18 +3321,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3344,7 +3341,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3352,10 +3349,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3364,7 +3361,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3372,10 +3369,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3384,18 +3381,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3404,18 +3401,18 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>237</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3424,18 +3421,18 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>237</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3444,18 +3441,18 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3464,7 +3461,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3472,10 +3469,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3484,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3492,10 +3489,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3504,7 +3501,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3512,10 +3509,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3524,7 +3521,7 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3532,10 +3529,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3544,7 +3541,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3552,10 +3549,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3564,18 +3561,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3584,18 +3581,18 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3604,7 +3601,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3612,10 +3609,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3624,7 +3621,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3632,10 +3629,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3644,7 +3641,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3652,10 +3649,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3664,7 +3661,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3672,10 +3669,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3684,7 +3681,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3692,10 +3689,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3704,7 +3701,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3712,10 +3709,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3724,7 +3721,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3732,10 +3729,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3744,7 +3741,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3752,21 +3749,61 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/TOY01D.xlsx
+++ b/E/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="293">
   <si>
     <t/>
   </si>
@@ -361,28 +361,427 @@
     <t>TG</t>
   </si>
   <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20143374</t>
+  </si>
+  <si>
+    <t>BARBIE SILICON POUCH</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
+  </si>
+  <si>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
     <t>20134460</t>
   </si>
   <si>
     <t>MEGA PKEMON POKEBALL</t>
   </si>
   <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
   </si>
   <si>
     <t>20092220</t>
@@ -391,331 +790,46 @@
     <t>PLAY DOH VALUE SET</t>
   </si>
   <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
     <t>20140768</t>
   </si>
   <si>
     <t>NT TRAVEL PET HOME</t>
   </si>
   <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
     <t>20127783</t>
   </si>
   <si>
     <t>APOLO HEAVY MACHNERY</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
   </si>
   <si>
     <t>20117276</t>
@@ -724,18 +838,48 @@
     <t>HOT WHLS PULL BACK</t>
   </si>
   <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20141255</t>
+  </si>
+  <si>
+    <t>BLOKEES TRANSFORMERS</t>
+  </si>
+  <si>
     <t>20095864</t>
   </si>
   <si>
     <t>WIKI D.CAST REAL CAR</t>
   </si>
   <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
     <t>20080091</t>
   </si>
   <si>
     <t>APOLO MSZ PULLBACK</t>
   </si>
   <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
     <t>20142227</t>
   </si>
   <si>
@@ -746,144 +890,6 @@
   </si>
   <si>
     <t>NT MY LOVELY PET</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20142150</t>
-  </si>
-  <si>
-    <t>BLOKEES BATMAN DV</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20141255</t>
-  </si>
-  <si>
-    <t>BLOKEES TRANSFORMERS</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2061,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2081,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2101,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2121,18 +2127,18 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2141,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2149,10 +2155,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2161,10 +2167,10 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,10 +2184,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2201,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2221,7 +2227,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2241,7 +2247,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2261,7 +2267,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2281,7 +2287,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2301,7 +2307,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2321,7 +2327,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2701,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>81</v>
@@ -2709,10 +2715,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2721,18 +2727,18 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2741,18 +2747,18 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2761,7 +2767,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2769,10 +2775,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2781,7 +2787,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2789,10 +2795,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2801,7 +2807,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2809,10 +2815,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2821,7 +2827,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2829,10 +2835,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2841,7 +2847,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2849,10 +2855,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2861,7 +2867,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2869,10 +2875,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2881,7 +2887,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2889,10 +2895,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2901,7 +2907,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2909,10 +2915,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2921,7 +2927,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2929,10 +2935,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2941,7 +2947,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2949,39 +2955,39 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2989,10 +2995,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3001,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>81</v>
@@ -3009,10 +3015,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3021,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3029,10 +3035,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3041,18 +3047,18 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3061,7 +3067,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3069,10 +3075,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3081,7 +3087,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3089,10 +3095,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3101,27 +3107,27 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3129,30 +3135,30 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3164,15 +3170,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>225</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3181,18 +3187,18 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>225</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3201,18 +3207,18 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3221,7 +3227,7 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3229,10 +3235,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3241,18 +3247,18 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3261,7 +3267,7 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3269,10 +3275,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3281,7 +3287,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3289,10 +3295,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3301,18 +3307,18 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3321,18 +3327,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3341,7 +3347,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3349,10 +3355,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3361,7 +3367,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3369,10 +3375,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3381,18 +3387,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3401,7 +3407,7 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3409,10 +3415,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3421,18 +3427,18 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3441,18 +3447,18 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3461,7 +3467,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3469,10 +3475,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3481,7 +3487,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3489,10 +3495,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3501,18 +3507,18 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3521,18 +3527,18 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3541,18 +3547,18 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3561,18 +3567,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3581,18 +3587,18 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3601,7 +3607,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3609,10 +3615,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3621,7 +3627,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3629,10 +3635,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3641,7 +3647,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3649,10 +3655,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3661,7 +3667,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3669,10 +3675,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3681,7 +3687,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3689,10 +3695,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3701,7 +3707,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3709,10 +3715,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3721,7 +3727,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3729,10 +3735,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3741,7 +3747,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3749,10 +3755,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3761,18 +3767,18 @@
         <v>23</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3781,29 +3787,9 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/TOY01D.xlsx
+++ b/E/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="296">
   <si>
     <t/>
   </si>
@@ -715,45 +715,45 @@
     <t>RT,(E-24B)</t>
   </si>
   <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
     <t>20134460</t>
   </si>
   <si>
     <t>MEGA PKEMON POKEBALL</t>
   </si>
   <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
     <t>20136677</t>
   </si>
   <si>
@@ -830,6 +830,15 @@
   </si>
   <si>
     <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
+    <t>20143747</t>
+  </si>
+  <si>
+    <t>EMCO MYSTERY DMPLG</t>
+  </si>
+  <si>
+    <t>PT,(E-45B)</t>
   </si>
   <si>
     <t>20117276</t>
@@ -1282,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2067,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2087,7 +2096,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2107,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2127,7 +2136,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>124</v>
@@ -2147,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2167,7 +2176,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>124</v>
@@ -3607,18 +3616,18 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3635,10 +3644,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3655,10 +3664,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3667,7 +3676,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3675,10 +3684,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3695,10 +3704,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3707,7 +3716,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3715,10 +3724,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3747,7 +3756,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3755,10 +3764,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3770,15 +3779,15 @@
         <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3787,9 +3796,29 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>
